--- a/用卷/2003.xlsx
+++ b/用卷/2003.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\高考用卷\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{530ED113-D4C9-4728-8A47-9DFE9906D27B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC61F958-B5E4-4871-9F1D-A63A8ED61990}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="76">
   <si>
     <t>年份</t>
   </si>
@@ -211,10 +211,6 @@
   </si>
   <si>
     <t>数学为江苏卷,语文、英语为全国卷,其他科目为新课程卷</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>数学为广东广西卷,语文、英语为全国卷,其他科目为旧课程卷</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
@@ -269,6 +265,26 @@
   <si>
     <t>新课程卷文理,旧课程卷文理,全国春考卷文理,北京春考卷文理,河南卷,辽宁卷,
 上海春考卷,秋考卷文理,江苏卷,广东广西卷</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>数学为粤桂卷,语文、英语为全国卷,其他科目为旧课程卷</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>说明</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>理综生物是新课程,物理化学是旧课程</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>理综生物是新旧课程,物理化学是旧课程</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>语文、英语为全国卷,其他科目为旧课程理综/文综卷</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -286,12 +302,14 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -299,12 +317,14 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="等线"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -366,7 +386,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -390,18 +410,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
@@ -413,16 +421,34 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -713,11 +739,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="22" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
       <c r="D1" s="7"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
@@ -730,7 +756,9 @@
       <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="2"/>
+      <c r="D2" s="10" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
@@ -742,7 +770,7 @@
       <c r="C3" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="D3" s="2"/>
+      <c r="D3" s="11"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
@@ -754,7 +782,7 @@
       <c r="C4" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="19"/>
+      <c r="D4" s="21"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
@@ -764,9 +792,9 @@
         <v>46</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="D5" s="19"/>
+        <v>66</v>
+      </c>
+      <c r="D5" s="21"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
@@ -776,9 +804,9 @@
         <v>42</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D6" s="2"/>
+        <v>59</v>
+      </c>
+      <c r="D6" s="11"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
@@ -788,9 +816,9 @@
         <v>4</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="D7" s="2"/>
+        <v>60</v>
+      </c>
+      <c r="D7" s="11"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
@@ -800,9 +828,9 @@
         <v>5</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="D8" s="8"/>
+        <v>63</v>
+      </c>
+      <c r="D8" s="10"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
@@ -812,9 +840,9 @@
         <v>54</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="D9" s="8"/>
+        <v>58</v>
+      </c>
+      <c r="D9" s="10"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
@@ -824,9 +852,9 @@
         <v>55</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="D10" s="2"/>
+        <v>60</v>
+      </c>
+      <c r="D10" s="11"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
@@ -838,7 +866,7 @@
       <c r="C11" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="D11" s="2"/>
+      <c r="D11" s="11"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
@@ -848,9 +876,9 @@
         <v>7</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="D12" s="2"/>
+        <v>60</v>
+      </c>
+      <c r="D12" s="11"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
@@ -860,9 +888,9 @@
         <v>8</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D13" s="2"/>
+        <v>61</v>
+      </c>
+      <c r="D13" s="11"/>
     </row>
     <row r="14" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
@@ -871,10 +899,10 @@
       <c r="B14" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="14" t="s">
+      <c r="C14" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="D14" s="16"/>
+      <c r="D14" s="18"/>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
@@ -883,8 +911,8 @@
       <c r="B15" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C15" s="15"/>
-      <c r="D15" s="17"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="19"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
@@ -896,7 +924,7 @@
       <c r="C16" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="D16" s="2"/>
+      <c r="D16" s="11"/>
     </row>
     <row r="17" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
@@ -906,9 +934,9 @@
         <v>41</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="D17" s="2"/>
+        <v>62</v>
+      </c>
+      <c r="D17" s="11"/>
     </row>
     <row r="18" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
@@ -918,9 +946,9 @@
         <v>48</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D18" s="2"/>
+        <v>57</v>
+      </c>
+      <c r="D18" s="11"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
@@ -930,9 +958,9 @@
         <v>49</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="D19" s="9"/>
+        <v>63</v>
+      </c>
+      <c r="D19" s="13"/>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
@@ -942,9 +970,9 @@
         <v>11</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="D20" s="2"/>
+        <v>62</v>
+      </c>
+      <c r="D20" s="11"/>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
@@ -954,9 +982,9 @@
         <v>12</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="D21" s="2"/>
+        <v>63</v>
+      </c>
+      <c r="D21" s="11"/>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
@@ -966,9 +994,9 @@
         <v>13</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="D22" s="2"/>
+        <v>63</v>
+      </c>
+      <c r="D22" s="11"/>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
@@ -978,9 +1006,9 @@
         <v>14</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="D23" s="2"/>
+        <v>62</v>
+      </c>
+      <c r="D23" s="11"/>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
@@ -990,9 +1018,9 @@
         <v>15</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="D24" s="2"/>
+        <v>62</v>
+      </c>
+      <c r="D24" s="11"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
@@ -1002,9 +1030,9 @@
         <v>16</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="D25" s="10"/>
+        <v>71</v>
+      </c>
+      <c r="D25" s="14"/>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
@@ -1014,9 +1042,9 @@
         <v>17</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="D26" s="10"/>
+        <v>71</v>
+      </c>
+      <c r="D26" s="14"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
@@ -1026,9 +1054,9 @@
         <v>18</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="D27" s="8"/>
+        <v>62</v>
+      </c>
+      <c r="D27" s="10"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
@@ -1038,9 +1066,9 @@
         <v>19</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="D28" s="2"/>
+        <v>62</v>
+      </c>
+      <c r="D28" s="11"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
@@ -1050,9 +1078,9 @@
         <v>20</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="D29" s="2"/>
+        <v>62</v>
+      </c>
+      <c r="D29" s="11"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
@@ -1062,9 +1090,11 @@
         <v>21</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="D30" s="11"/>
+        <v>64</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
@@ -1074,9 +1104,11 @@
         <v>22</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D31" s="2"/>
+        <v>65</v>
+      </c>
+      <c r="D31" s="15" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
@@ -1086,9 +1118,9 @@
         <v>23</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="D32" s="2"/>
+        <v>62</v>
+      </c>
+      <c r="D32" s="11"/>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
@@ -1098,9 +1130,9 @@
         <v>24</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="D33" s="8"/>
+        <v>62</v>
+      </c>
+      <c r="D33" s="10"/>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
@@ -1110,9 +1142,9 @@
         <v>45</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="D34" s="2"/>
+        <v>62</v>
+      </c>
+      <c r="D34" s="11"/>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
@@ -1122,9 +1154,9 @@
         <v>25</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="D35" s="2"/>
+        <v>61</v>
+      </c>
+      <c r="D35" s="10"/>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
@@ -1134,9 +1166,9 @@
         <v>26</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="D36" s="2"/>
+        <v>62</v>
+      </c>
+      <c r="D36" s="11"/>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
@@ -1145,24 +1177,24 @@
       <c r="B37" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C37" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="D37" s="2"/>
+      <c r="C37" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="D37" s="11"/>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A38" s="13"/>
-      <c r="B38" s="13"/>
+      <c r="A38" s="9"/>
+      <c r="B38" s="9"/>
       <c r="C38" s="1"/>
       <c r="D38" s="2"/>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A39" s="18" t="s">
+      <c r="A39" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="B39" s="18"/>
-      <c r="C39" s="18"/>
-      <c r="D39" s="12"/>
+      <c r="B39" s="20"/>
+      <c r="C39" s="20"/>
+      <c r="D39" s="8"/>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
@@ -1174,7 +1206,7 @@
       <c r="C40" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D40" s="12"/>
+      <c r="D40" s="8"/>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
@@ -1184,9 +1216,9 @@
         <v>6</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="D41" s="12"/>
+        <v>67</v>
+      </c>
+      <c r="D41" s="8"/>
     </row>
     <row r="42" spans="1:4" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
@@ -1196,9 +1228,9 @@
         <v>16</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="D42" s="12"/>
+        <v>70</v>
+      </c>
+      <c r="D42" s="8"/>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
@@ -1208,33 +1240,33 @@
         <v>6</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="D43" s="12"/>
+        <v>67</v>
+      </c>
+      <c r="D43" s="8"/>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
         <v>35</v>
       </c>
       <c r="B44" s="4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="D44" s="12"/>
+        <v>68</v>
+      </c>
+      <c r="D44" s="8"/>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
         <v>36</v>
       </c>
       <c r="B45" s="4">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="D45" s="12"/>
+        <v>68</v>
+      </c>
+      <c r="D45" s="8"/>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46" s="3" t="s">
@@ -1244,9 +1276,9 @@
         <v>8</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="D46" s="12"/>
+        <v>69</v>
+      </c>
+      <c r="D46" s="8"/>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47" s="3" t="s">
@@ -1256,9 +1288,9 @@
         <v>6</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="D47" s="12"/>
+        <v>68</v>
+      </c>
+      <c r="D47" s="8"/>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48" s="3" t="s">
@@ -1268,9 +1300,9 @@
         <v>6</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="D48" s="12"/>
+        <v>68</v>
+      </c>
+      <c r="D48" s="8"/>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49" s="3" t="s">
@@ -1280,9 +1312,9 @@
         <v>6</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="D49" s="12"/>
+        <v>68</v>
+      </c>
+      <c r="D49" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="5">
